--- a/docs/harness/wirelist/DRB102-pin-table.xlsx
+++ b/docs/harness/wirelist/DRB102-pin-table.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Black/White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>Black/White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Black/White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>Black/Blue</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>Black/White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Black/Blue</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>Black/White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Black/Blue</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Orange/White</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Black/White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>Black/Blue</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>Black/White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M75" s="5" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Black/White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>Black/Blue</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Red/Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>Red/Black</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="M79" s="5" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M85" s="5" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">

--- a/docs/harness/wirelist/DRB102-pin-table.xlsx
+++ b/docs/harness/wirelist/DRB102-pin-table.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -702,14 +702,14 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I4" s="6" t="n"/>
@@ -737,14 +737,14 @@
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I5" s="6" t="n"/>
@@ -772,14 +772,14 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I6" s="6" t="n"/>
@@ -807,14 +807,14 @@
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -842,14 +842,14 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
@@ -877,14 +877,14 @@
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine 2</t>
+          <t>Fuel pressure sensor (sensor block, LH firewall) 2</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1542,14 +1542,14 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I20" s="6" t="n"/>
@@ -1577,14 +1577,14 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I21" s="6" t="n"/>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine 3</t>
+          <t>Coolant pressure sensor (rear of block, LH) 2</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine 1</t>
+          <t>Oil pressure sensor (sensor block, LH firewall) 2</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2494,14 +2494,14 @@
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I36" s="6" t="n"/>
@@ -2529,14 +2529,14 @@
       <c r="D37" s="6" t="n"/>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I37" s="6" t="n"/>
@@ -2564,14 +2564,14 @@
       <c r="D38" s="6" t="n"/>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F38" s="6" t="n"/>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I38" s="6" t="n"/>
@@ -2599,14 +2599,14 @@
       <c r="D39" s="6" t="n"/>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F39" s="6" t="n"/>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I39" s="6" t="n"/>
@@ -2634,14 +2634,14 @@
       <c r="D40" s="6" t="n"/>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F40" s="6" t="n"/>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I40" s="6" t="n"/>
@@ -2669,14 +2669,14 @@
       <c r="D41" s="6" t="n"/>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F41" s="6" t="n"/>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I41" s="6" t="n"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2830,14 +2830,14 @@
       <c r="D44" s="6" t="n"/>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F44" s="6" t="n"/>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I44" s="6" t="n"/>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3117,14 +3117,14 @@
       <c r="D49" s="6" t="n"/>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F49" s="6" t="n"/>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I49" s="6" t="n"/>
@@ -3152,14 +3152,14 @@
       <c r="D50" s="6" t="n"/>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F50" s="6" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I50" s="6" t="n"/>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -3250,14 +3250,14 @@
       <c r="D52" s="6" t="n"/>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F52" s="6" t="n"/>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I52" s="6" t="n"/>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3411,14 +3411,14 @@
       <c r="D55" s="6" t="n"/>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F55" s="6" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I55" s="6" t="n"/>
@@ -3446,14 +3446,14 @@
       <c r="D56" s="6" t="n"/>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F56" s="6" t="n"/>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I56" s="6" t="n"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3733,14 +3733,14 @@
       <c r="D61" s="6" t="n"/>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F61" s="6" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I61" s="6" t="n"/>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3831,14 +3831,14 @@
       <c r="D63" s="6" t="n"/>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F63" s="6" t="n"/>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I63" s="6" t="n"/>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -5059,14 +5059,14 @@
       <c r="D83" s="6" t="n"/>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F83" s="6" t="n"/>
       <c r="G83" s="7" t="n"/>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I83" s="6" t="n"/>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -5283,14 +5283,14 @@
       <c r="D87" s="6" t="n"/>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F87" s="6" t="n"/>
       <c r="G87" s="7" t="n"/>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I87" s="6" t="n"/>
@@ -5318,14 +5318,14 @@
       <c r="D88" s="6" t="n"/>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F88" s="6" t="n"/>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I88" s="6" t="n"/>
@@ -5353,14 +5353,14 @@
       <c r="D89" s="6" t="n"/>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F89" s="6" t="n"/>
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I89" s="6" t="n"/>
@@ -5388,14 +5388,14 @@
       <c r="D90" s="6" t="n"/>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F90" s="6" t="n"/>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I90" s="6" t="n"/>
@@ -5423,14 +5423,14 @@
       <c r="D91" s="6" t="n"/>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F91" s="6" t="n"/>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I91" s="6" t="n"/>
@@ -5458,14 +5458,14 @@
       <c r="D92" s="6" t="n"/>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F92" s="6" t="n"/>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I92" s="6" t="n"/>
@@ -5493,14 +5493,14 @@
       <c r="D93" s="6" t="n"/>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F93" s="6" t="n"/>
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I93" s="6" t="n"/>
@@ -5528,14 +5528,14 @@
       <c r="D94" s="6" t="n"/>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F94" s="6" t="n"/>
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I94" s="6" t="n"/>
@@ -5563,14 +5563,14 @@
       <c r="D95" s="6" t="n"/>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F95" s="6" t="n"/>
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I95" s="6" t="n"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -5724,14 +5724,14 @@
       <c r="D98" s="6" t="n"/>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F98" s="6" t="n"/>
       <c r="G98" s="7" t="n"/>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I98" s="6" t="n"/>
@@ -5759,14 +5759,14 @@
       <c r="D99" s="6" t="n"/>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F99" s="6" t="n"/>
       <c r="G99" s="7" t="n"/>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I99" s="6" t="n"/>
@@ -5794,14 +5794,14 @@
       <c r="D100" s="6" t="n"/>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F100" s="6" t="n"/>
       <c r="G100" s="7" t="n"/>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I100" s="6" t="n"/>
@@ -5829,14 +5829,14 @@
       <c r="D101" s="6" t="n"/>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F101" s="6" t="n"/>
       <c r="G101" s="7" t="n"/>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I101" s="6" t="n"/>
@@ -5864,14 +5864,14 @@
       <c r="D102" s="6" t="n"/>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F102" s="6" t="n"/>
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I102" s="6" t="n"/>
@@ -5899,14 +5899,14 @@
       <c r="D103" s="6" t="n"/>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F103" s="6" t="n"/>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I103" s="6" t="n"/>

--- a/docs/harness/wirelist/DRB102-pin-table.xlsx
+++ b/docs/harness/wirelist/DRB102-pin-table.xlsx
@@ -1178,7 +1178,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>+5V BUS 6</t>
+          <t>BUS-5V 6</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+          <t>BUS-GNDOUT-B 8</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>+5V BUS 3</t>
+          <t>BUS-5V 3</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS 6</t>
+          <t>BUS-GNDOUT-A 6</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>+5V BUS 7</t>
+          <t>BUS-5V 7</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>+5V BUS 5</t>
+          <t>BUS-5V 5</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+          <t>BUS-GNDOUT-B 7</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS 2</t>
+          <t>BUS-GNDOUT-A 2</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>+5V BUS 2</t>
+          <t>BUS-5V 2</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>+5V BUS 4</t>
+          <t>BUS-5V 4</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS 5</t>
+          <t>BUS-GNDOUT-A 5</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS 4</t>
+          <t>BUS-GNDOUT-A 4</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+          <t>BUS-GNDOUT-B 6</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS 3</t>
+          <t>BUS-GNDOUT-A 3</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/DRB102-pin-table.xlsx
+++ b/docs/harness/wirelist/DRB102-pin-table.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -702,14 +702,14 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I4" s="6" t="n"/>
@@ -737,14 +737,14 @@
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I5" s="6" t="n"/>
@@ -772,14 +772,14 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I6" s="6" t="n"/>
@@ -807,14 +807,14 @@
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -842,14 +842,14 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
@@ -877,14 +877,14 @@
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>+5V BUS 6</t>
+          <t>BUS-5V 6</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine 2</t>
+          <t>Fuel pressure sensor (sensor block, LH firewall) 2</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+          <t>BUS-GNDOUT-B 8</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>+5V BUS 3</t>
+          <t>BUS-5V 3</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS 6</t>
+          <t>BUS-GNDOUT-A 6</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1542,14 +1542,14 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I20" s="6" t="n"/>
@@ -1577,14 +1577,14 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I21" s="6" t="n"/>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>+5V BUS 7</t>
+          <t>BUS-5V 7</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine 3</t>
+          <t>Coolant pressure sensor (rear of block, LH) 2</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>+5V BUS 5</t>
+          <t>BUS-5V 5</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>IX-B-RAIL inline plug, +5 V to B-engine 1</t>
+          <t>Oil pressure sensor (sensor block, LH firewall) 2</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+          <t>BUS-GNDOUT-B 7</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS 2</t>
+          <t>BUS-GNDOUT-A 2</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2494,14 +2494,14 @@
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I36" s="6" t="n"/>
@@ -2529,14 +2529,14 @@
       <c r="D37" s="6" t="n"/>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I37" s="6" t="n"/>
@@ -2564,14 +2564,14 @@
       <c r="D38" s="6" t="n"/>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F38" s="6" t="n"/>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I38" s="6" t="n"/>
@@ -2599,14 +2599,14 @@
       <c r="D39" s="6" t="n"/>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F39" s="6" t="n"/>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I39" s="6" t="n"/>
@@ -2634,14 +2634,14 @@
       <c r="D40" s="6" t="n"/>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F40" s="6" t="n"/>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I40" s="6" t="n"/>
@@ -2669,14 +2669,14 @@
       <c r="D41" s="6" t="n"/>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F41" s="6" t="n"/>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I41" s="6" t="n"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>+5V BUS 2</t>
+          <t>BUS-5V 2</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2830,14 +2830,14 @@
       <c r="D44" s="6" t="n"/>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F44" s="6" t="n"/>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I44" s="6" t="n"/>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3117,14 +3117,14 @@
       <c r="D49" s="6" t="n"/>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F49" s="6" t="n"/>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I49" s="6" t="n"/>
@@ -3152,14 +3152,14 @@
       <c r="D50" s="6" t="n"/>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F50" s="6" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I50" s="6" t="n"/>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -3250,14 +3250,14 @@
       <c r="D52" s="6" t="n"/>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F52" s="6" t="n"/>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I52" s="6" t="n"/>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>+5V BUS 4</t>
+          <t>BUS-5V 4</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3411,14 +3411,14 @@
       <c r="D55" s="6" t="n"/>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F55" s="6" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I55" s="6" t="n"/>
@@ -3446,14 +3446,14 @@
       <c r="D56" s="6" t="n"/>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F56" s="6" t="n"/>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I56" s="6" t="n"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS 5</t>
+          <t>BUS-GNDOUT-A 5</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3733,14 +3733,14 @@
       <c r="D61" s="6" t="n"/>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F61" s="6" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I61" s="6" t="n"/>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3831,14 +3831,14 @@
       <c r="D63" s="6" t="n"/>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F63" s="6" t="n"/>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I63" s="6" t="n"/>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS 4</t>
+          <t>BUS-GNDOUT-A 4</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+          <t>BUS-GNDOUT-B 6</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS 3</t>
+          <t>BUS-GNDOUT-A 3</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -5059,14 +5059,14 @@
       <c r="D83" s="6" t="n"/>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F83" s="6" t="n"/>
       <c r="G83" s="7" t="n"/>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I83" s="6" t="n"/>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -5283,14 +5283,14 @@
       <c r="D87" s="6" t="n"/>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F87" s="6" t="n"/>
       <c r="G87" s="7" t="n"/>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I87" s="6" t="n"/>
@@ -5318,14 +5318,14 @@
       <c r="D88" s="6" t="n"/>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F88" s="6" t="n"/>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I88" s="6" t="n"/>
@@ -5353,14 +5353,14 @@
       <c r="D89" s="6" t="n"/>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F89" s="6" t="n"/>
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I89" s="6" t="n"/>
@@ -5388,14 +5388,14 @@
       <c r="D90" s="6" t="n"/>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F90" s="6" t="n"/>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I90" s="6" t="n"/>
@@ -5423,14 +5423,14 @@
       <c r="D91" s="6" t="n"/>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F91" s="6" t="n"/>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I91" s="6" t="n"/>
@@ -5458,14 +5458,14 @@
       <c r="D92" s="6" t="n"/>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F92" s="6" t="n"/>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I92" s="6" t="n"/>
@@ -5493,14 +5493,14 @@
       <c r="D93" s="6" t="n"/>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F93" s="6" t="n"/>
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I93" s="6" t="n"/>
@@ -5528,14 +5528,14 @@
       <c r="D94" s="6" t="n"/>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F94" s="6" t="n"/>
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I94" s="6" t="n"/>
@@ -5563,14 +5563,14 @@
       <c r="D95" s="6" t="n"/>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F95" s="6" t="n"/>
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I95" s="6" t="n"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
     </row>
@@ -5724,14 +5724,14 @@
       <c r="D98" s="6" t="n"/>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F98" s="6" t="n"/>
       <c r="G98" s="7" t="n"/>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I98" s="6" t="n"/>
@@ -5759,14 +5759,14 @@
       <c r="D99" s="6" t="n"/>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F99" s="6" t="n"/>
       <c r="G99" s="7" t="n"/>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I99" s="6" t="n"/>
@@ -5794,14 +5794,14 @@
       <c r="D100" s="6" t="n"/>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F100" s="6" t="n"/>
       <c r="G100" s="7" t="n"/>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I100" s="6" t="n"/>
@@ -5829,14 +5829,14 @@
       <c r="D101" s="6" t="n"/>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F101" s="6" t="n"/>
       <c r="G101" s="7" t="n"/>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I101" s="6" t="n"/>
@@ -5864,14 +5864,14 @@
       <c r="D102" s="6" t="n"/>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F102" s="6" t="n"/>
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I102" s="6" t="n"/>
@@ -5899,14 +5899,14 @@
       <c r="D103" s="6" t="n"/>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F103" s="6" t="n"/>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>B-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="I103" s="6" t="n"/>
